--- a/output/pdf_financials_xlsx/FAS.xlsx
+++ b/output/pdf_financials_xlsx/FAS.xlsx
@@ -6785,22 +6785,22 @@
         <v>0.04416</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.3371</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>3.211917</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>3.367949</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>3.518862</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>3.780738</v>
       </c>
       <c r="T92" s="3" t="n">
-        <v>0</v>
+        <v>4.31174</v>
       </c>
     </row>
     <row r="93">
@@ -11244,7 +11244,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -12298,7 +12302,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -13267,7 +13275,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/FAS.xlsx
+++ b/output/pdf_financials_xlsx/FAS.xlsx
@@ -1137,19 +1137,19 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.018833</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.027234</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.000871</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>0.0008899999999999999</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>0</v>
+        <v>0.012045</v>
       </c>
     </row>
     <row r="13">
@@ -2229,19 +2229,19 @@
         </is>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-4.789383</v>
+        <v>-4.808216</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-3.09566</v>
+        <v>-3.122894</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-5.680914</v>
+        <v>-5.681785</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-0.482135</v>
+        <v>-0.483025</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>-1.028323</v>
+        <v>-1.040368</v>
       </c>
     </row>
     <row r="28">
@@ -2359,19 +2359,19 @@
         </is>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-4.789383</v>
+        <v>-4.808216</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-3.09566</v>
+        <v>-3.122894</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-5.680914</v>
+        <v>-5.681785</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-0.482135</v>
+        <v>-0.483025</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>-1.028323</v>
+        <v>-1.040368</v>
       </c>
     </row>
     <row r="30">
@@ -2668,55 +2668,55 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.191196</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.108216</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.033893</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.017813</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.0006089999999999999</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.001945</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.007107</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.050228</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.57281</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.498077</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.412725</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.246569</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>4.579522</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.338729</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.010575</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.929216</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>0</v>
+        <v>1.911223</v>
       </c>
     </row>
     <row r="35">
@@ -2804,55 +2804,55 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.191196</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.108216</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.033893</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.017813</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.0006089999999999999</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.001945</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.007107</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.050228</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.57281</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.498077</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.412725</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.246569</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>4.579522</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.338729</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.010575</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.929216</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>0</v>
+        <v>1.911223</v>
       </c>
     </row>
     <row r="37">
@@ -3653,22 +3653,22 @@
         <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>8.632697</v>
+        <v>8.386127999999999</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>4.622739</v>
+        <v>0.043217</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.402364</v>
+        <v>0.063635</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.019637</v>
+        <v>0.009062000000000001</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.949744</v>
+        <v>0.020528</v>
       </c>
       <c r="T48" s="3" t="n">
-        <v>1.948232</v>
+        <v>0.037009</v>
       </c>
     </row>
     <row r="49">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -16803,7 +16803,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -19174,7 +19174,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -21826,7 +21826,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -37708,7 +37708,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -37815,7 +37815,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -44843,7 +44843,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
